--- a/notebooks/OMP_stuff_for_Manuel/RREX_WMTYPES_5poly_ORIGINAL.xlsx
+++ b/notebooks/OMP_stuff_for_Manuel/RREX_WMTYPES_5poly_ORIGINAL.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399BF978-767B-4FC1-9116-18305CB7D5D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="11500" xr2:uid="{55C3EF8E-6B26-4C61-893E-38A87239426C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{55C3EF8E-6B26-4C61-893E-38A87239426C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -474,16 +474,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5534A5F-E9E6-40C7-9BD6-42148A7D753A}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.7109375" customWidth="1"/>
-    <col min="7" max="7" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.7265625" customWidth="1"/>
+    <col min="7" max="7" width="32.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -498,7 +498,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -521,7 +521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -544,7 +544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -567,7 +567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -590,7 +590,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -610,7 +610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -630,7 +630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -653,49 +653,49 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
